--- a/data/reports/CRYSTALLIZED_COMBINATIONS.xlsx
+++ b/data/reports/CRYSTALLIZED_COMBINATIONS.xlsx
@@ -516,15 +516,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"REENTRY_GR_HLHH_MODE": "HH", "GOLDEN_RULE_HTF_MIN_TFS": "3", "GOLDEN_RULE_MIN_</t>
+          <t>{"GOLDEN_RULE_HTF_MIN_TFS": "3", "GOLDEN_RULE_MIN_IND": "3", "KINDERGARTEN_EMA_G</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-4.39</v>
+        <v>-0.48</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>REENTRY_GR_HLHH_MODE + GOLDEN_RULE_HTF_MIN_TFS</t>
+          <t>GOLDEN_RULE_HTF_MIN_TFS + KINDERGARTEN_EMA_GATE_ENABLED + WT_DC_EXIT_THRESHOLD + REENTRY_GR_HLHH_MODE</t>
         </is>
       </c>
       <c r="D2" t="b">
@@ -534,15 +534,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>{"GOLDEN_RULE_HTF_MIN_TFS": "3", "GOLDEN_RULE_MIN_IND": "3", "REENTRY_GR_HLHH_MO</t>
+          <t>{"KINDERGARTEN_EMA_GATE_ENABLED": "False", "KINDERGARTEN_TF": "15m", "KINDERGART</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-4.39</v>
+        <v>-0.48</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GOLDEN_RULE_HTF_MIN_TFS + REENTRY_GR_HLHH_MODE</t>
+          <t>KINDERGARTEN_EMA_GATE_ENABLED + GOLDEN_RULE_HTF_MIN_TFS + WT_DC_EXIT_THRESHOLD + REENTRY_GR_HLHH_MODE</t>
         </is>
       </c>
       <c r="D3" t="b">
@@ -552,15 +552,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>{"REENTRY_GR_HLHH_MODE": "HH", "WT_DC_EXIT_THRESHOLD": "45", "COOLDOWN_BARS_15m"</t>
+          <t>{"KINDERGARTEN_EMA_GATE_ENABLED": "False", "KINDERGARTEN_TF": "15m", "KINDERGART</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-5.23</v>
+        <v>-0.48</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>REENTRY_GR_HLHH_MODE + WT_DC_EXIT_THRESHOLD</t>
+          <t>KINDERGARTEN_EMA_GATE_ENABLED + WT_DC_EXIT_THRESHOLD + GOLDEN_RULE_HTF_MIN_TFS + REENTRY_GR_HLHH_MODE</t>
         </is>
       </c>
       <c r="D4" t="b">
@@ -570,15 +570,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{"WT_DC_EXIT_THRESHOLD": "45", "COOLDOWN_BARS_15m": "3", "REENTRY_GR_HLHH_MODE":</t>
+          <t>{"WT_DC_EXIT_THRESHOLD": "45", "COOLDOWN_BARS_15m": "3", "KINDERGARTEN_EMA_GATE_</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-5.23</v>
+        <v>-0.48</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WT_DC_EXIT_THRESHOLD + REENTRY_GR_HLHH_MODE</t>
+          <t>WT_DC_EXIT_THRESHOLD + KINDERGARTEN_EMA_GATE_ENABLED + GOLDEN_RULE_HTF_MIN_TFS + REENTRY_GR_HLHH_MODE</t>
         </is>
       </c>
       <c r="D5" t="b">
@@ -588,15 +588,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>{"GOLDEN_RULE_HTF_MIN_TFS": "3", "GOLDEN_RULE_MIN_IND": "3", "KINDERGARTEN_EMA_G</t>
+          <t>{"GOLDEN_RULE_HTF_MIN_TFS": "3", "GOLDEN_RULE_MIN_IND": "3", "WT_DC_EXIT_THRESHO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-5.41</v>
+        <v>-0.48</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GOLDEN_RULE_HTF_MIN_TFS + KINDERGARTEN_EMA_GATE_ENABLED</t>
+          <t>GOLDEN_RULE_HTF_MIN_TFS + WT_DC_EXIT_THRESHOLD + KINDERGARTEN_EMA_GATE_ENABLED + REENTRY_GR_HLHH_MODE</t>
         </is>
       </c>
       <c r="D6" t="b">
@@ -606,15 +606,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{"KINDERGARTEN_EMA_GATE_ENABLED": "False", "KINDERGARTEN_TF": "15m", "KINDERGART</t>
+          <t>{"WT_DC_EXIT_THRESHOLD": "45", "COOLDOWN_BARS_15m": "3", "GOLDEN_RULE_HTF_MIN_TF</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-5.41</v>
+        <v>-0.48</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KINDERGARTEN_EMA_GATE_ENABLED + GOLDEN_RULE_HTF_MIN_TFS</t>
+          <t>WT_DC_EXIT_THRESHOLD + GOLDEN_RULE_HTF_MIN_TFS + KINDERGARTEN_EMA_GATE_ENABLED + REENTRY_GR_HLHH_MODE</t>
         </is>
       </c>
       <c r="D7" t="b">
@@ -624,15 +624,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>{"GOLDEN_RULE_HTF_MIN_TFS": "3", "GOLDEN_RULE_MIN_IND": "3", "WT_DC_EXIT_THRESHO</t>
+          <t>{"GOLDEN_RULE_HTF_MIN_TFS": "3", "GOLDEN_RULE_MIN_IND": "3", "KINDERGARTEN_EMA_G</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-5.47</v>
+        <v>-0.48</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GOLDEN_RULE_HTF_MIN_TFS + WT_DC_EXIT_THRESHOLD</t>
+          <t>GOLDEN_RULE_HTF_MIN_TFS + KINDERGARTEN_EMA_GATE_ENABLED + REENTRY_GR_HLHH_MODE + WT_DC_EXIT_THRESHOLD</t>
         </is>
       </c>
       <c r="D8" t="b">
@@ -642,15 +642,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>{"WT_DC_EXIT_THRESHOLD": "45", "COOLDOWN_BARS_15m": "3", "GOLDEN_RULE_HTF_MIN_TF</t>
+          <t>{"KINDERGARTEN_EMA_GATE_ENABLED": "False", "KINDERGARTEN_TF": "15m", "KINDERGART</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-5.47</v>
+        <v>-0.48</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WT_DC_EXIT_THRESHOLD + GOLDEN_RULE_HTF_MIN_TFS</t>
+          <t>KINDERGARTEN_EMA_GATE_ENABLED + GOLDEN_RULE_HTF_MIN_TFS + REENTRY_GR_HLHH_MODE + WT_DC_EXIT_THRESHOLD</t>
         </is>
       </c>
       <c r="D9" t="b">
@@ -660,15 +660,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>{"REENTRY_GR_HLHH_MODE": "HH", "KINDERGARTEN_EMA_GATE_ENABLED": "False", "KINDER</t>
+          <t>{"REENTRY_GR_HLHH_MODE": "HH", "GOLDEN_RULE_HTF_MIN_TFS": "3", "GOLDEN_RULE_MIN_</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-5.83</v>
+        <v>-0.48</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>REENTRY_GR_HLHH_MODE + KINDERGARTEN_EMA_GATE_ENABLED</t>
+          <t>REENTRY_GR_HLHH_MODE + GOLDEN_RULE_HTF_MIN_TFS + KINDERGARTEN_EMA_GATE_ENABLED + WT_DC_EXIT_THRESHOLD</t>
         </is>
       </c>
       <c r="D10" t="b">
@@ -678,15 +678,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>{"KINDERGARTEN_EMA_GATE_ENABLED": "False", "KINDERGARTEN_TF": "15m", "KINDERGART</t>
+          <t>{"GOLDEN_RULE_HTF_MIN_TFS": "3", "GOLDEN_RULE_MIN_IND": "3", "REENTRY_GR_HLHH_MO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-5.83</v>
+        <v>-0.48</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KINDERGARTEN_EMA_GATE_ENABLED + REENTRY_GR_HLHH_MODE</t>
+          <t>GOLDEN_RULE_HTF_MIN_TFS + REENTRY_GR_HLHH_MODE + KINDERGARTEN_EMA_GATE_ENABLED + WT_DC_EXIT_THRESHOLD</t>
         </is>
       </c>
       <c r="D11" t="b">
